--- a/Data/effectiveness.xlsx
+++ b/Data/effectiveness.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\makinoyuuki\Desktop\ICSME2026\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{349C7040-10F1-4779-ADAF-1857E04F772B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{726A80B1-8139-4CA9-8F6A-C2CCFE761276}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="10890" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -158,56 +158,45 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>UI Component Integrity: Frontend Layout Verification</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Privileged Access: Admin Authentication for Approval Workflow</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Workflow Execution: State-based Request Revocation</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Integration Setup: API Token Generation and Capture</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Onboarding Workflow: Context-aware Company Registration</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Data Privacy: Role-Based Access Control Column Filtering</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Client-Side Validation: Asymmetric Date Range Logic</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Entity Persistence: Sequential CRUD for Holiday Management</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Resource Constraint: Post-Audit Session Cleanup</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Temporal Data Entry: Historical Start Date Configuration</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Session Management: Multi-user Session Termination</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Event Management: Multi-modal Lifecycle and Dynamic Reordering</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Relational Navigation: Hierarchical Topics and Event Linking</t>
-    <phoneticPr fontId="1"/>
+    <t>Frontend Layout Verification</t>
+  </si>
+  <si>
+    <t>Multi-modal Reordering</t>
+  </si>
+  <si>
+    <t>Hierarchical Topic &amp; Event</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Admin Approval Authentication</t>
+  </si>
+  <si>
+    <t>State-based Request Revocation</t>
+  </si>
+  <si>
+    <t>API Token Generation &amp; Capture</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Historical Start Date Configuration</t>
+  </si>
+  <si>
+    <t>Multi-user Session Termination</t>
+  </si>
+  <si>
+    <t>Context-aware Registration</t>
+  </si>
+  <si>
+    <t>RBAC Column Filtering</t>
+  </si>
+  <si>
+    <t>Asymmetric Date Range</t>
+  </si>
+  <si>
+    <t>CRUD for Holiday Management</t>
+  </si>
+  <si>
+    <t>Post-Audit Session Cleanup</t>
   </si>
 </sst>
 </file>
@@ -402,15 +391,6 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
@@ -419,6 +399,15 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
@@ -711,16 +700,19 @@
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="19.25" customWidth="1"/>
-    <col min="2" max="2" width="100.08203125" customWidth="1"/>
+    <col min="2" max="2" width="44.5" customWidth="1"/>
     <col min="3" max="3" width="161.83203125" customWidth="1"/>
     <col min="4" max="4" width="13.4140625" customWidth="1"/>
     <col min="5" max="5" width="12.6640625" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
     <col min="7" max="8" width="20.4140625" customWidth="1"/>
-    <col min="9" max="9" width="31" customWidth="1"/>
+    <col min="9" max="9" width="22.5" customWidth="1"/>
     <col min="10" max="10" width="20.1640625" customWidth="1"/>
-    <col min="11" max="14" width="31" customWidth="1"/>
-    <col min="15" max="15" width="34.08203125" customWidth="1"/>
+    <col min="11" max="11" width="19.33203125" customWidth="1"/>
+    <col min="12" max="12" width="20.4140625" customWidth="1"/>
+    <col min="13" max="13" width="27.33203125" customWidth="1"/>
+    <col min="14" max="14" width="22.08203125" customWidth="1"/>
+    <col min="15" max="15" width="18.1640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="21.5" customHeight="1" thickBot="1">
@@ -771,7 +763,7 @@
       </c>
     </row>
     <row r="2" spans="1:15" ht="22.5" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="9" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -824,11 +816,11 @@
       </c>
     </row>
     <row r="3" spans="1:15" ht="24.5" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="10" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>5</v>
@@ -842,44 +834,44 @@
       <c r="F3" s="3">
         <v>1</v>
       </c>
-      <c r="G3" s="10">
+      <c r="G3" s="7">
         <f t="shared" ref="G3:G14" si="1">D3/(D3+E3)</f>
         <v>1</v>
       </c>
-      <c r="H3" s="10">
+      <c r="H3" s="7">
         <f t="shared" ref="H3:H14" si="2">D3/(D3+F3)</f>
         <v>0.875</v>
       </c>
-      <c r="I3" s="10">
+      <c r="I3" s="7">
         <f t="shared" si="0"/>
         <v>0.93333333333333335</v>
       </c>
-      <c r="J3" s="9">
+      <c r="J3" s="6">
         <v>401</v>
       </c>
-      <c r="K3" s="9">
-        <v>0</v>
-      </c>
-      <c r="L3" s="9">
+      <c r="K3" s="6">
+        <v>0</v>
+      </c>
+      <c r="L3" s="6">
         <v>9</v>
       </c>
-      <c r="M3" s="10">
-        <f t="shared" ref="M3:M14" si="3">J3/(J3+K3)</f>
-        <v>1</v>
-      </c>
-      <c r="N3" s="10">
-        <f t="shared" ref="N3:N14" si="4">J3/(J3+L3)</f>
+      <c r="M3" s="7">
+        <f t="shared" ref="M3:M13" si="3">J3/(J3+K3)</f>
+        <v>1</v>
+      </c>
+      <c r="N3" s="7">
+        <f t="shared" ref="N3:N13" si="4">J3/(J3+L3)</f>
         <v>0.97804878048780486</v>
       </c>
-      <c r="O3" s="10">
-        <f t="shared" ref="O3:O14" si="5">2*(M3*N3)/(M3+N3)</f>
+      <c r="O3" s="7">
+        <f t="shared" ref="O3:O13" si="5">2*(M3*N3)/(M3+N3)</f>
         <v>0.98890258939580766</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="24" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A4" s="7"/>
+      <c r="A4" s="11"/>
       <c r="B4" s="4" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>6</v>
@@ -928,11 +920,11 @@
       </c>
     </row>
     <row r="5" spans="1:15" ht="25" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="10" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>10</v>
@@ -946,44 +938,44 @@
       <c r="F5" s="3">
         <v>0</v>
       </c>
-      <c r="G5" s="10">
+      <c r="G5" s="7">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="H5" s="10">
+      <c r="H5" s="7">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="I5" s="10">
+      <c r="I5" s="7">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="J5" s="9">
+      <c r="J5" s="6">
         <v>28</v>
       </c>
-      <c r="K5" s="9">
-        <v>0</v>
-      </c>
-      <c r="L5" s="9">
-        <v>0</v>
-      </c>
-      <c r="M5" s="10">
+      <c r="K5" s="6">
+        <v>0</v>
+      </c>
+      <c r="L5" s="6">
+        <v>0</v>
+      </c>
+      <c r="M5" s="7">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="N5" s="10">
+      <c r="N5" s="7">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="O5" s="10">
+      <c r="O5" s="7">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="30.5" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A6" s="8"/>
+      <c r="A6" s="12"/>
       <c r="B6" s="4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>11</v>
@@ -1029,9 +1021,9 @@
       </c>
     </row>
     <row r="7" spans="1:15" ht="24" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A7" s="8"/>
+      <c r="A7" s="12"/>
       <c r="B7" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>12</v>
@@ -1045,41 +1037,41 @@
       <c r="F7" s="3">
         <v>0</v>
       </c>
-      <c r="G7" s="10">
+      <c r="G7" s="7">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="H7" s="10">
+      <c r="H7" s="7">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="I7" s="10">
+      <c r="I7" s="7">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="J7" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="K7" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="L7" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="M7" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="N7" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="O7" s="9" t="s">
+      <c r="J7" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L7" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="M7" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="N7" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="O7" s="6" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:15" ht="24.5" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A8" s="8"/>
+      <c r="A8" s="12"/>
       <c r="B8" s="4" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>13</v>
@@ -1128,9 +1120,9 @@
       </c>
     </row>
     <row r="9" spans="1:15" ht="29" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A9" s="8"/>
-      <c r="B9" s="11" t="s">
-        <v>42</v>
+      <c r="A9" s="12"/>
+      <c r="B9" s="8" t="s">
+        <v>39</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>14</v>
@@ -1144,41 +1136,41 @@
       <c r="F9" s="3">
         <v>0</v>
       </c>
-      <c r="G9" s="10">
+      <c r="G9" s="7">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="H9" s="10">
+      <c r="H9" s="7">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="I9" s="10">
+      <c r="I9" s="7">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="J9" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="K9" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="L9" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="M9" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="N9" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="O9" s="9" t="s">
+      <c r="J9" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L9" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="M9" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="N9" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="O9" s="6" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="25.5" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A10" s="8"/>
+      <c r="A10" s="12"/>
       <c r="B10" s="4" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>8</v>
@@ -1227,9 +1219,9 @@
       </c>
     </row>
     <row r="11" spans="1:15" ht="26" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A11" s="8"/>
-      <c r="B11" s="9" t="s">
-        <v>37</v>
+      <c r="A11" s="12"/>
+      <c r="B11" s="6" t="s">
+        <v>41</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>15</v>
@@ -1243,44 +1235,44 @@
       <c r="F11" s="3">
         <v>0</v>
       </c>
-      <c r="G11" s="10">
+      <c r="G11" s="7">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="H11" s="10">
+      <c r="H11" s="7">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="I11" s="10">
+      <c r="I11" s="7">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="J11" s="9">
+      <c r="J11" s="6">
         <v>28</v>
       </c>
-      <c r="K11" s="9">
-        <v>0</v>
-      </c>
-      <c r="L11" s="9">
-        <v>0</v>
-      </c>
-      <c r="M11" s="10">
+      <c r="K11" s="6">
+        <v>0</v>
+      </c>
+      <c r="L11" s="6">
+        <v>0</v>
+      </c>
+      <c r="M11" s="7">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="N11" s="10">
+      <c r="N11" s="7">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="O11" s="10">
+      <c r="O11" s="7">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:15" ht="27.5" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A12" s="8"/>
+      <c r="A12" s="12"/>
       <c r="B12" s="4" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>16</v>
@@ -1326,9 +1318,9 @@
       </c>
     </row>
     <row r="13" spans="1:15" ht="23.5" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A13" s="8"/>
-      <c r="B13" s="9" t="s">
-        <v>39</v>
+      <c r="A13" s="12"/>
+      <c r="B13" s="6" t="s">
+        <v>43</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>9</v>
@@ -1342,44 +1334,44 @@
       <c r="F13" s="3">
         <v>0</v>
       </c>
-      <c r="G13" s="10">
+      <c r="G13" s="7">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="H13" s="10">
+      <c r="H13" s="7">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="I13" s="10">
+      <c r="I13" s="7">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="J13" s="9">
+      <c r="J13" s="6">
         <v>14</v>
       </c>
-      <c r="K13" s="9">
-        <v>0</v>
-      </c>
-      <c r="L13" s="9">
-        <v>0</v>
-      </c>
-      <c r="M13" s="10">
+      <c r="K13" s="6">
+        <v>0</v>
+      </c>
+      <c r="L13" s="6">
+        <v>0</v>
+      </c>
+      <c r="M13" s="7">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="N13" s="10">
+      <c r="N13" s="7">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="O13" s="10">
+      <c r="O13" s="7">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:15" ht="32.5" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A14" s="7"/>
+      <c r="A14" s="11"/>
       <c r="B14" s="4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>17</v>
